--- a/career_roadmap_dataset.xlsx
+++ b/career_roadmap_dataset.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Prem Kumar\Projects\Career Roadmap Generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7EE514-1C0C-4339-A3A5-36ABB9022A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD34064-BD50-4315-A231-78C89F9A7DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="348" yWindow="528" windowWidth="12768" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="job_descriptions" sheetId="1" r:id="rId1"/>
     <sheet name="courses" sheetId="2" r:id="rId2"/>
     <sheet name="certifications" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2284" uniqueCount="698">
   <si>
     <t>Job Title</t>
   </si>
@@ -762,6 +762,1365 @@
   </si>
   <si>
     <t>$180k-$260k</t>
+  </si>
+  <si>
+    <t>Google Associate Cloud Engineer</t>
+  </si>
+  <si>
+    <t>Microsoft Azure AI Engineer</t>
+  </si>
+  <si>
+    <t>$165</t>
+  </si>
+  <si>
+    <t>AWS Solutions Architect Associate</t>
+  </si>
+  <si>
+    <t>Certified Data Professional (CDP)</t>
+  </si>
+  <si>
+    <t>ICCP</t>
+  </si>
+  <si>
+    <t>$395</t>
+  </si>
+  <si>
+    <t>Offensive Security OSCP</t>
+  </si>
+  <si>
+    <t>Offensive Security</t>
+  </si>
+  <si>
+    <t>$1499</t>
+  </si>
+  <si>
+    <t>Certified Information Systems Security (CISSP)</t>
+  </si>
+  <si>
+    <t>ISC2</t>
+  </si>
+  <si>
+    <t>$699</t>
+  </si>
+  <si>
+    <t>Kubernetes Administrator (CKA)</t>
+  </si>
+  <si>
+    <t>Linux Foundation</t>
+  </si>
+  <si>
+    <t>HashiCorp Terraform Associate</t>
+  </si>
+  <si>
+    <t>HashiCorp</t>
+  </si>
+  <si>
+    <t>$70</t>
+  </si>
+  <si>
+    <t>Databricks Certified Associate Developer</t>
+  </si>
+  <si>
+    <t>dbt Analytics Engineer Certification</t>
+  </si>
+  <si>
+    <t>dbt Labs</t>
+  </si>
+  <si>
+    <t>Snowflake SnowPro Core</t>
+  </si>
+  <si>
+    <t>$175</t>
+  </si>
+  <si>
+    <t>Microsoft Power BI Data Analyst</t>
+  </si>
+  <si>
+    <t>Tableau Desktop Specialist</t>
+  </si>
+  <si>
+    <t>Tableau/Salesforce</t>
+  </si>
+  <si>
+    <t>$250</t>
+  </si>
+  <si>
+    <t>1 month</t>
+  </si>
+  <si>
+    <t>Google Professional ML Engineer</t>
+  </si>
+  <si>
+    <t>NVIDIA DLI Fundamentals of Deep Learning</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>$30</t>
+  </si>
+  <si>
+    <t>1 week</t>
+  </si>
+  <si>
+    <t>Hugging Face NLP Certificate</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>Kaggle ML Certificate</t>
+  </si>
+  <si>
+    <t>Kaggle</t>
+  </si>
+  <si>
+    <t>Self-paced</t>
+  </si>
+  <si>
+    <t>PIAIC AI Certificate</t>
+  </si>
+  <si>
+    <t>PIAIC Pakistan</t>
+  </si>
+  <si>
+    <t>PKR 40k total</t>
+  </si>
+  <si>
+    <t>1 year</t>
+  </si>
+  <si>
+    <t>CompTIA Network+</t>
+  </si>
+  <si>
+    <t>$358</t>
+  </si>
+  <si>
+    <t>EC-Council CHFI</t>
+  </si>
+  <si>
+    <t>$999</t>
+  </si>
+  <si>
+    <t>Machine Learning Crash Course</t>
+  </si>
+  <si>
+    <t>Google (Free)</t>
+  </si>
+  <si>
+    <t>developers.google.com/machine-learning/crash-course</t>
+  </si>
+  <si>
+    <t>15 hours</t>
+  </si>
+  <si>
+    <t>CS229 Machine Learning (Stanford)</t>
+  </si>
+  <si>
+    <t>YouTube (Free)</t>
+  </si>
+  <si>
+    <t>youtube.com/watch?v=jGwO_UgTS7I</t>
+  </si>
+  <si>
+    <t>Intro to Machine Learning</t>
+  </si>
+  <si>
+    <t>Kaggle (Free)</t>
+  </si>
+  <si>
+    <t>kaggle.com/learn/intro-to-machine-learning</t>
+  </si>
+  <si>
+    <t>5 hours</t>
+  </si>
+  <si>
+    <t>Python for Everybody</t>
+  </si>
+  <si>
+    <t>Coursera (Audit Free)</t>
+  </si>
+  <si>
+    <t>coursera.org/specializations/python</t>
+  </si>
+  <si>
+    <t>IBM Data Science Professional</t>
+  </si>
+  <si>
+    <t>coursera.org/professional-certificates/ibm-data-science</t>
+  </si>
+  <si>
+    <t>Statistics with Python</t>
+  </si>
+  <si>
+    <t>coursera.org/specializations/statistics-with-python</t>
+  </si>
+  <si>
+    <t>Data Analysis with Python</t>
+  </si>
+  <si>
+    <t>freeCodeCamp (Free)</t>
+  </si>
+  <si>
+    <t>freecodecamp.org/learn/data-analysis-with-python</t>
+  </si>
+  <si>
+    <t>300 hours</t>
+  </si>
+  <si>
+    <t>Google Advanced Data Analytics</t>
+  </si>
+  <si>
+    <t>coursera.org/professional-certificates/google-advanced-data-analytics</t>
+  </si>
+  <si>
+    <t>SQL Tutorial</t>
+  </si>
+  <si>
+    <t>W3Schools / Mode (Free)</t>
+  </si>
+  <si>
+    <t>mode.com/sql-tutorial</t>
+  </si>
+  <si>
+    <t>2 weeks</t>
+  </si>
+  <si>
+    <t>CS50 Web Programming</t>
+  </si>
+  <si>
+    <t>edX (Audit Free)</t>
+  </si>
+  <si>
+    <t>cs50.harvard.edu/web</t>
+  </si>
+  <si>
+    <t>12 weeks</t>
+  </si>
+  <si>
+    <t>Full Stack Open</t>
+  </si>
+  <si>
+    <t>University of Helsinki (Free)</t>
+  </si>
+  <si>
+    <t>fullstackopen.com</t>
+  </si>
+  <si>
+    <t>The Odin Project</t>
+  </si>
+  <si>
+    <t>theOdinProject (Free)</t>
+  </si>
+  <si>
+    <t>theodinproject.com</t>
+  </si>
+  <si>
+    <t>12 months</t>
+  </si>
+  <si>
+    <t>Responsive Web Design</t>
+  </si>
+  <si>
+    <t>freecodecamp.org/learn/2022/responsive-web-design</t>
+  </si>
+  <si>
+    <t>Node.js Tutorial</t>
+  </si>
+  <si>
+    <t>YouTube - Traversy (Free)</t>
+  </si>
+  <si>
+    <t>youtube.com/nodejs-crash-course</t>
+  </si>
+  <si>
+    <t>1 day</t>
+  </si>
+  <si>
+    <t>Django for Beginners</t>
+  </si>
+  <si>
+    <t>YouTube - Corey Schafer (Free)</t>
+  </si>
+  <si>
+    <t>youtube.com/django-tutorial</t>
+  </si>
+  <si>
+    <t>MLOps Fundamentals</t>
+  </si>
+  <si>
+    <t>Google Cloud (Free)</t>
+  </si>
+  <si>
+    <t>cloudskillsboost.google/course_templates</t>
+  </si>
+  <si>
+    <t>20 hours</t>
+  </si>
+  <si>
+    <t>Intro to MLflow</t>
+  </si>
+  <si>
+    <t>MLflow Docs (Free)</t>
+  </si>
+  <si>
+    <t>mlflow.org/docs/latest/tutorials-and-examples</t>
+  </si>
+  <si>
+    <t>Cybersecurity for Everyone</t>
+  </si>
+  <si>
+    <t>coursera.org/learn/cybersecurity-for-everyone</t>
+  </si>
+  <si>
+    <t>Ethical Hacking Basics</t>
+  </si>
+  <si>
+    <t>YouTube - NetworkChuck (Free)</t>
+  </si>
+  <si>
+    <t>youtube.com/networkchuck-hacking</t>
+  </si>
+  <si>
+    <t>Google Cybersecurity Certificate</t>
+  </si>
+  <si>
+    <t>coursera.org/professional-certificates/google-cybersecurity</t>
+  </si>
+  <si>
+    <t>NLP with Python (NLTK Book)</t>
+  </si>
+  <si>
+    <t>NLTK.org (Free)</t>
+  </si>
+  <si>
+    <t>nltk.org/book</t>
+  </si>
+  <si>
+    <t>Hugging Face NLP Course</t>
+  </si>
+  <si>
+    <t>Hugging Face (Free)</t>
+  </si>
+  <si>
+    <t>huggingface.co/learn/nlp-course</t>
+  </si>
+  <si>
+    <t>Fast.ai Practical Deep Learning</t>
+  </si>
+  <si>
+    <t>fast.ai (Free)</t>
+  </si>
+  <si>
+    <t>course.fast.ai</t>
+  </si>
+  <si>
+    <t>Deep Learning.AI Short Courses</t>
+  </si>
+  <si>
+    <t>deeplearning.ai/short-courses</t>
+  </si>
+  <si>
+    <t>2-4 hours each</t>
+  </si>
+  <si>
+    <t>LangChain for LLM Apps</t>
+  </si>
+  <si>
+    <t>YouTube + Docs (Free)</t>
+  </si>
+  <si>
+    <t>youtube.com/langchain-tutorial</t>
+  </si>
+  <si>
+    <t>CS50 Introduction to AI</t>
+  </si>
+  <si>
+    <t>cs50.harvard.edu/ai</t>
+  </si>
+  <si>
+    <t>7 weeks</t>
+  </si>
+  <si>
+    <t>Data Engineering Zoomcamp</t>
+  </si>
+  <si>
+    <t>DataTalks.Club (Free)</t>
+  </si>
+  <si>
+    <t>github.com/DataTalks-Club/data-engineering-zoomcamp</t>
+  </si>
+  <si>
+    <t>9 weeks</t>
+  </si>
+  <si>
+    <t>Fundamentals of Data Engineering</t>
+  </si>
+  <si>
+    <t>YouTube - Andreas Kretz (Free)</t>
+  </si>
+  <si>
+    <t>youtube.com/playwithdata</t>
+  </si>
+  <si>
+    <t>PIAIC AI Quarter 1</t>
+  </si>
+  <si>
+    <t>PIAIC (Free/Low Cost)</t>
+  </si>
+  <si>
+    <t>piaic.org</t>
+  </si>
+  <si>
+    <t>PIAIC Cloud Quarter 2</t>
+  </si>
+  <si>
+    <t>Digiskills Python</t>
+  </si>
+  <si>
+    <t>DigiSkills.pk (Free)</t>
+  </si>
+  <si>
+    <t>digiskills.pk</t>
+  </si>
+  <si>
+    <t>Digiskills Web Development</t>
+  </si>
+  <si>
+    <t>Digiskills Digital Marketing</t>
+  </si>
+  <si>
+    <t>Saylani Tech Bootcamp</t>
+  </si>
+  <si>
+    <t>Saylani Welfare (Free)</t>
+  </si>
+  <si>
+    <t>saylaniwelfare.com/smit</t>
+  </si>
+  <si>
+    <t>NAVTTC AI &amp; ML Course</t>
+  </si>
+  <si>
+    <t>NAVTTC (Free)</t>
+  </si>
+  <si>
+    <t>navttc.gov.pk</t>
+  </si>
+  <si>
+    <t>AWS Certified Solutions Architect</t>
+  </si>
+  <si>
+    <t>udemy.com/course/aws-certified-solutions-architect</t>
+  </si>
+  <si>
+    <t>Tableau Training</t>
+  </si>
+  <si>
+    <t>udemy.com/course/tableau-training</t>
+  </si>
+  <si>
+    <t>Power BI Masterclass</t>
+  </si>
+  <si>
+    <t>udemy.com/course/microsoft-power-bi-masterclass</t>
+  </si>
+  <si>
+    <t>Apache Spark with Python</t>
+  </si>
+  <si>
+    <t>udemy.com/course/apache-spark-with-python-big-data</t>
+  </si>
+  <si>
+    <t>10 weeks</t>
+  </si>
+  <si>
+    <t>Kubernetes for Developers</t>
+  </si>
+  <si>
+    <t>udemy.com/course/docker-and-kubernetes-the-complete-guide</t>
+  </si>
+  <si>
+    <t>React - The Complete Guide</t>
+  </si>
+  <si>
+    <t>udemy.com/course/react-the-complete-guide</t>
+  </si>
+  <si>
+    <t>16 weeks</t>
+  </si>
+  <si>
+    <t>System Design Interview Prep</t>
+  </si>
+  <si>
+    <t>educative.io</t>
+  </si>
+  <si>
+    <t>educative.io/courses/grokking-the-system-design-interview</t>
+  </si>
+  <si>
+    <t>Natural Language Processing Specialization</t>
+  </si>
+  <si>
+    <t>coursera.org/specializations/natural-language-processing</t>
+  </si>
+  <si>
+    <t>LLM Engineering</t>
+  </si>
+  <si>
+    <t>udemy.com/course/llm-engineering</t>
+  </si>
+  <si>
+    <t>Computer Vision Nanodegree</t>
+  </si>
+  <si>
+    <t>Udacity</t>
+  </si>
+  <si>
+    <t>udacity.com/course/computer-vision-nanodegree</t>
+  </si>
+  <si>
+    <t>Certified Kubernetes Admin Prep</t>
+  </si>
+  <si>
+    <t>training.linuxfoundation.org/certification/cka</t>
+  </si>
+  <si>
+    <t>Penetration Testing Bootcamp</t>
+  </si>
+  <si>
+    <t>TCM Security</t>
+  </si>
+  <si>
+    <t>academy.tcm-sec.com</t>
+  </si>
+  <si>
+    <t>Zero to Mastery - Machine Learning</t>
+  </si>
+  <si>
+    <t>ZTM Academy</t>
+  </si>
+  <si>
+    <t>zerotomastery.io/courses/machine-learning</t>
+  </si>
+  <si>
+    <t>Reinforcement Learning Specialization</t>
+  </si>
+  <si>
+    <t>coursera.org/specializations/reinforcement-learning</t>
+  </si>
+  <si>
+    <t>dbt Fundamentals</t>
+  </si>
+  <si>
+    <t>dbt Labs (Free)</t>
+  </si>
+  <si>
+    <t>courses.getdbt.com</t>
+  </si>
+  <si>
+    <t>Systems Limited</t>
+  </si>
+  <si>
+    <t>Python, TensorFlow, Scikit-learn, Docker, REST APIs, Git, SQL, NumPy, Pandas, Feature Engineering, Model Deployment</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>PKR 150k-250k</t>
+  </si>
+  <si>
+    <t>IT Services</t>
+  </si>
+  <si>
+    <t>Teradata Pakistan</t>
+  </si>
+  <si>
+    <t>Python, SQL, Statistics, Pandas, Machine Learning, Tableau, Hypothesis Testing, Data Wrangling, BigQuery, Regression Analysis</t>
+  </si>
+  <si>
+    <t>PKR 120k-200k</t>
+  </si>
+  <si>
+    <t>HBL (Habib Bank Limited)</t>
+  </si>
+  <si>
+    <t>SQL, Excel, Power BI, Financial Reporting, KPI Tracking, Pivot Tables, DAX Formulas, Dashboard Design, Data Cleaning</t>
+  </si>
+  <si>
+    <t>PKR 60k-100k</t>
+  </si>
+  <si>
+    <t>Netsol Technologies</t>
+  </si>
+  <si>
+    <t>Java, Spring Boot, PostgreSQL, REST APIs, Docker, Microservices, Git, Linux, Leasing Software, FATCA Compliance</t>
+  </si>
+  <si>
+    <t>PKR 200k-350k</t>
+  </si>
+  <si>
+    <t>Tkxel</t>
+  </si>
+  <si>
+    <t>React, Node.js, MongoDB, AWS, Tailwind CSS, TypeScript, REST APIs, Docker, CI/CD, Agile, Jest Testing</t>
+  </si>
+  <si>
+    <t>PKR 150k-280k</t>
+  </si>
+  <si>
+    <t>Arbisoft</t>
+  </si>
+  <si>
+    <t>Python, MLflow, Docker, Kubernetes, AWS, GitHub Actions, Model Monitoring, FastAPI, CI/CD, Linux</t>
+  </si>
+  <si>
+    <t>PKR 160k-280k</t>
+  </si>
+  <si>
+    <t>Jazz (Veon Pakistan)</t>
+  </si>
+  <si>
+    <t>Network Security, SIEM, Linux, Penetration Testing, Firewalls, OWASP Top 10, Vulnerability Assessment, Wireshark, Python</t>
+  </si>
+  <si>
+    <t>PKR 130k-220k</t>
+  </si>
+  <si>
+    <t>Telecom</t>
+  </si>
+  <si>
+    <t>10Pearls</t>
+  </si>
+  <si>
+    <t>Python, Spark, Airflow, SQL, ETL, AWS, dbt, Data Modeling, PostgreSQL, Docker, Data Quality</t>
+  </si>
+  <si>
+    <t>PKR 150k-260k</t>
+  </si>
+  <si>
+    <t>Contour Software</t>
+  </si>
+  <si>
+    <t>Python, Transformers, PyTorch, BERT, Text Classification, NLP Pipelines, SpaCy, Hugging Face, REST APIs, Docker</t>
+  </si>
+  <si>
+    <t>Afiniti</t>
+  </si>
+  <si>
+    <t>LLMs, LangChain, Python, Prompt Engineering, RAG, Vector Databases, FastAPI, Docker, Fine Tuning, Embeddings</t>
+  </si>
+  <si>
+    <t>PKR 250k-450k</t>
+  </si>
+  <si>
+    <t>Programmers Force</t>
+  </si>
+  <si>
+    <t>React, Django, PostgreSQL, Docker, REST APIs, TypeScript, AWS, Git, CI/CD, Redis</t>
+  </si>
+  <si>
+    <t>PKR 130k-240k</t>
+  </si>
+  <si>
+    <t>MCB Bank</t>
+  </si>
+  <si>
+    <t>SQL, Excel, Power BI, Risk Analytics, Financial Reporting, Credit Scoring, Compliance, Data Cleaning, DAX</t>
+  </si>
+  <si>
+    <t>PKR 55k-90k</t>
+  </si>
+  <si>
+    <t>Folio3 Software</t>
+  </si>
+  <si>
+    <t>Python, Django, REST APIs, PostgreSQL, AWS, Docker, Redis, Celery, Unit Testing, Git, Linux</t>
+  </si>
+  <si>
+    <t>PKR 140k-250k</t>
+  </si>
+  <si>
+    <t>MTBC (CureMD)</t>
+  </si>
+  <si>
+    <t>Python, TensorFlow, Medical Data, NLP, Feature Engineering, Scikit-learn, REST APIs, Docker, AWS, Healthcare AI</t>
+  </si>
+  <si>
+    <t>Softech Worldwide</t>
+  </si>
+  <si>
+    <t>Python, OpenCV, PyTorch, CNNs, Object Detection, YOLO, Image Processing, C++, TensorRT, Edge AI</t>
+  </si>
+  <si>
+    <t>Zones LLC (Pakistan)</t>
+  </si>
+  <si>
+    <t>Python, Machine Learning, SQL, Pandas, Statistics, Scikit-learn, Data Visualization, Power BI, A/B Testing</t>
+  </si>
+  <si>
+    <t>PKR 80k-140k</t>
+  </si>
+  <si>
+    <t>DevOps Engineer</t>
+  </si>
+  <si>
+    <t>Inbox Business Technologies</t>
+  </si>
+  <si>
+    <t>Docker, Kubernetes, CI/CD, AWS, Terraform, Linux, Jenkins, Ansible, Monitoring, Git, Shell Scripting</t>
+  </si>
+  <si>
+    <t>PKR 150k-270k</t>
+  </si>
+  <si>
+    <t>AI Engineer</t>
+  </si>
+  <si>
+    <t>VentureDive</t>
+  </si>
+  <si>
+    <t>Python, LLMs, LangChain, FastAPI, Docker, AWS, RAG, Embeddings, Prompt Engineering, Fine Tuning</t>
+  </si>
+  <si>
+    <t>PKR 180k-300k</t>
+  </si>
+  <si>
+    <t>Techlogix</t>
+  </si>
+  <si>
+    <t>Python, Airflow, Spark, SQL, AWS, ETL, dbt, Data Warehousing, PostgreSQL, Delta Lake</t>
+  </si>
+  <si>
+    <t>Epista Life Science</t>
+  </si>
+  <si>
+    <t>React, Node.js, TypeScript, PostgreSQL, Docker, AWS, GraphQL, CI/CD, Agile, REST APIs</t>
+  </si>
+  <si>
+    <t>PKR 200k-380k</t>
+  </si>
+  <si>
+    <t>Salesforce</t>
+  </si>
+  <si>
+    <t>Python, PyTorch, NLP, CRM AI, REST APIs, MLflow, Feature Engineering, A/B Testing, AWS, Model Deployment</t>
+  </si>
+  <si>
+    <t>Palantir</t>
+  </si>
+  <si>
+    <t>Python, SQL, Graph Analytics, Data Modeling, Statistics, Pandas, Spark, AWS, Tableau, Stakeholder Communication</t>
+  </si>
+  <si>
+    <t>$140k-$195k</t>
+  </si>
+  <si>
+    <t>Walmart</t>
+  </si>
+  <si>
+    <t>SQL, Tableau, Excel, Power BI, Retail Analytics, Supply Chain Data, A/B Testing, KPI Tracking, Python</t>
+  </si>
+  <si>
+    <t>$68k-$95k</t>
+  </si>
+  <si>
+    <t>PayPal</t>
+  </si>
+  <si>
+    <t>Java, Spring Boot, REST APIs, PostgreSQL, Kafka, Redis, Microservices, Payment Processing, OAuth2, Docker</t>
+  </si>
+  <si>
+    <t>$145k-$195k</t>
+  </si>
+  <si>
+    <t>Atlassian</t>
+  </si>
+  <si>
+    <t>React, TypeScript, Node.js, PostgreSQL, Docker, Kubernetes, GraphQL, REST APIs, CI/CD, Agile</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>$110k-$150k AUD</t>
+  </si>
+  <si>
+    <t>Python, Kubeflow, Docker, GCP, Airflow, MLflow, Model Monitoring, Feature Store, Spark, BigQuery</t>
+  </si>
+  <si>
+    <t>Azure Security, SIEM, Penetration Testing, Zero Trust, Python, Threat Intelligence, MITRE ATT&amp;CK, Cloud Security</t>
+  </si>
+  <si>
+    <t>BERT, GPT, Python, TensorFlow, Text Classification, Sequence Models, Alexa NLU, Named Entity Recognition, SpaCy</t>
+  </si>
+  <si>
+    <t>$135k-$175k</t>
+  </si>
+  <si>
+    <t>Python, Spark, Kafka, Airflow, SQL, Hadoop, Data Lake, Hive, dbt, Data Quality, BigQuery</t>
+  </si>
+  <si>
+    <t>$145k-$185k</t>
+  </si>
+  <si>
+    <t>Google Brain</t>
+  </si>
+  <si>
+    <t>Python, JAX, TPUs, Research Writing, Large Scale ML, Neural Architecture, Meta Learning, Scaling Laws</t>
+  </si>
+  <si>
+    <t>LLMs, Azure OpenAI, LangChain, Python, RAG, Semantic Kernel, Vector DBs, Prompt Engineering, Fine Tuning</t>
+  </si>
+  <si>
+    <t>React, TypeScript, Go, PostgreSQL, REST APIs, GraphQL, Docker, Payment UX, Accessibility, Testing</t>
+  </si>
+  <si>
+    <t>$155k-$200k</t>
+  </si>
+  <si>
+    <t>Samsung Research</t>
+  </si>
+  <si>
+    <t>Python, PyTorch, On-device ML, TensorFlow Lite, Model Compression, C++, Android AI, Quantization</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>$130k-$180k</t>
+  </si>
+  <si>
+    <t>Booking.com</t>
+  </si>
+  <si>
+    <t>Python, SQL, Causal Inference, A/B Testing, Statistics, Machine Learning, Hadoop, Spark, Personalization</t>
+  </si>
+  <si>
+    <t>Grab</t>
+  </si>
+  <si>
+    <t>Go, Python, Microservices, Kafka, PostgreSQL, Redis, Docker, Kubernetes, REST APIs, gRPC</t>
+  </si>
+  <si>
+    <t>Singapore</t>
+  </si>
+  <si>
+    <t>$120k-$165k SGD</t>
+  </si>
+  <si>
+    <t>Revolut</t>
+  </si>
+  <si>
+    <t>SQL, Python, Tableau, Looker, Financial Analytics, Fraud Analytics, Product Analytics, A/B Testing, dbt</t>
+  </si>
+  <si>
+    <t>Waymo</t>
+  </si>
+  <si>
+    <t>Python, Kubeflow, Docker, GCP, CI/CD, Data Versioning, Model Registry, Autonomous Vehicle ML Pipeline</t>
+  </si>
+  <si>
+    <t>$165k-$220k</t>
+  </si>
+  <si>
+    <t>Mobileye</t>
+  </si>
+  <si>
+    <t>Python, C++, OpenCV, CNNs, ADAS, LiDAR, Sensor Fusion, Real-time Systems, CUDA, Object Detection</t>
+  </si>
+  <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>KPMG</t>
+  </si>
+  <si>
+    <t>Risk Assessment, SIEM, Compliance, ISO 27001, Penetration Testing, Cloud Security, Incident Response</t>
+  </si>
+  <si>
+    <t>$95k-$130k</t>
+  </si>
+  <si>
+    <t>Python, Spark, Airflow, dbt, SQL, Data Modeling, BigQuery, Real-time Pipelines, Data Quality</t>
+  </si>
+  <si>
+    <t>Canva</t>
+  </si>
+  <si>
+    <t>React, TypeScript, Node.js, Go, PostgreSQL, GraphQL, Design Systems, Performance Optimization, AWS</t>
+  </si>
+  <si>
+    <t>$115k-$150k AUD</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Cohere</t>
+  </si>
+  <si>
+    <t>Python, LLMs, RAG, Fine Tuning, Embeddings, NLP, REST APIs, Docker, Evaluation Frameworks</t>
+  </si>
+  <si>
+    <t>$130k-$175k CAD</t>
+  </si>
+  <si>
+    <t>Bytedance</t>
+  </si>
+  <si>
+    <t>Python, PyTorch, Recommendation Systems, Large Scale ML, Ads Ranking, Feature Engineering, A/B Testing</t>
+  </si>
+  <si>
+    <t>$165k-$225k</t>
+  </si>
+  <si>
+    <t>Klarna</t>
+  </si>
+  <si>
+    <t>Python, SQL, Credit Scoring, Fraud Detection, Statistics, Machine Learning, Causal Inference, Experimentation</t>
+  </si>
+  <si>
+    <t>$105k-$140k</t>
+  </si>
+  <si>
+    <t>Wise</t>
+  </si>
+  <si>
+    <t>Python, Django, PostgreSQL, REST APIs, Kafka, Docker, Financial APIs, PCI DSS, Redis, Microservices</t>
+  </si>
+  <si>
+    <t>$100k-$135k</t>
+  </si>
+  <si>
+    <t>Kubernetes, Terraform, AWS, CI/CD, Spinnaker, Chaos Engineering, Python, Monitoring, Linux</t>
+  </si>
+  <si>
+    <t>$155k-$205k</t>
+  </si>
+  <si>
+    <t>Adobe</t>
+  </si>
+  <si>
+    <t>Python, LLMs, Diffusion Models, LangChain, Prompt Engineering, RAG, Creative AI, Fine Tuning, APIs</t>
+  </si>
+  <si>
+    <t>$160k-$220k</t>
+  </si>
+  <si>
+    <t>Tesco</t>
+  </si>
+  <si>
+    <t>SQL, Power BI, Excel, Retail Analytics, Customer Segmentation, Supply Chain Analytics, Python, Tableau</t>
+  </si>
+  <si>
+    <t>£35k-£50k</t>
+  </si>
+  <si>
+    <t>Baidu</t>
+  </si>
+  <si>
+    <t>Python, PyTorch, Chinese NLP, ERNIE, Text Generation, Machine Translation, Sentiment Analysis</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>Python, PyTorch, OpenCV, 3D Detection, LiDAR, Camera, Sensor Fusion, CUDA, Real-time Inference</t>
+  </si>
+  <si>
+    <t>Noon (UAE)</t>
+  </si>
+  <si>
+    <t>Python, Scikit-learn, Recommendation Systems, SQL, AWS, Docker, Feature Engineering, A/B Testing</t>
+  </si>
+  <si>
+    <t>UAE</t>
+  </si>
+  <si>
+    <t>AED 18k-30k/mo</t>
+  </si>
+  <si>
+    <t>Careem</t>
+  </si>
+  <si>
+    <t>Python, Spark, Airflow, Kafka, AWS, dbt, SQL, Data Pipelines, PostgreSQL, Data Quality</t>
+  </si>
+  <si>
+    <t>AED 20k-35k/mo</t>
+  </si>
+  <si>
+    <t>talabat</t>
+  </si>
+  <si>
+    <t>Node.js, MongoDB, REST APIs, Redis, Docker, Kubernetes, Microservices, AWS, Kafka, gRPC</t>
+  </si>
+  <si>
+    <t>AED 25k-40k/mo</t>
+  </si>
+  <si>
+    <t>Food Delivery</t>
+  </si>
+  <si>
+    <t>Dubizzle</t>
+  </si>
+  <si>
+    <t>React, Node.js, PostgreSQL, Docker, AWS, TypeScript, REST APIs, GraphQL, CI/CD, Redis</t>
+  </si>
+  <si>
+    <t>AED 18k-32k/mo</t>
+  </si>
+  <si>
+    <t>Marketplace</t>
+  </si>
+  <si>
+    <t>Emirates NBD</t>
+  </si>
+  <si>
+    <t>Python, SQL, Risk Modeling, Credit Analytics, Machine Learning, Statistics, Power BI, Fraud Detection</t>
+  </si>
+  <si>
+    <t>AED 22k-38k/mo</t>
+  </si>
+  <si>
+    <t>Etisalat (e&amp;)</t>
+  </si>
+  <si>
+    <t>Network Security, SIEM, Penetration Testing, Zero Trust, Firewalls, Cloud Security, Python, Incident Response</t>
+  </si>
+  <si>
+    <t>AED 28k-45k/mo</t>
+  </si>
+  <si>
+    <t>G42 (UAE)</t>
+  </si>
+  <si>
+    <t>Python, LLMs, PyTorch, Fine Tuning, RAG, LangChain, Vector DBs, FastAPI, Docker, Prompt Engineering</t>
+  </si>
+  <si>
+    <t>AED 30k-50k/mo</t>
+  </si>
+  <si>
+    <t>Telenor Pakistan</t>
+  </si>
+  <si>
+    <t>SQL, Power BI, Excel, Telecom Analytics, Customer Analytics, KPI Reporting, Python, Tableau</t>
+  </si>
+  <si>
+    <t>PKR 65k-105k</t>
+  </si>
+  <si>
+    <t>Meezan Bank</t>
+  </si>
+  <si>
+    <t>Java, Spring Boot, REST APIs, Oracle DB, Docker, Microservices, Banking APIs, PCI DSS, XML</t>
+  </si>
+  <si>
+    <t>PKR 140k-240k</t>
+  </si>
+  <si>
+    <t>Confiz</t>
+  </si>
+  <si>
+    <t>Python, TensorFlow, NLP, Feature Engineering, Scikit-learn, Docker, REST APIs, AWS, SQL</t>
+  </si>
+  <si>
+    <t>Iterate.ai Pakistan</t>
+  </si>
+  <si>
+    <t>Python, dbt, Airflow, Spark, SQL, GCP, BigQuery, Data Modeling, ETL, Data Quality</t>
+  </si>
+  <si>
+    <t>Devsinc</t>
+  </si>
+  <si>
+    <t>Python, LLMs, LangChain, OpenAI API, RAG, Vector DBs, Prompt Engineering, FastAPI, Docker</t>
+  </si>
+  <si>
+    <t>PKR 100k-180k</t>
+  </si>
+  <si>
+    <t>NextBridge</t>
+  </si>
+  <si>
+    <t>React, Node.js, PostgreSQL, Docker, REST APIs, TypeScript, AWS, CI/CD, Tailwind CSS</t>
+  </si>
+  <si>
+    <t>PKR 90k-150k</t>
+  </si>
+  <si>
+    <t>U Microfinance Bank</t>
+  </si>
+  <si>
+    <t>SQL, Excel, Power BI, Financial Analytics, Credit Reporting, KPI Tracking, Dashboard Design</t>
+  </si>
+  <si>
+    <t>PTCL</t>
+  </si>
+  <si>
+    <t>Network Security, SIEM, Vulnerability Assessment, Linux, Python, Firewalls, Log Analysis, ISO 27001</t>
+  </si>
+  <si>
+    <t>PKR 70k-115k</t>
+  </si>
+  <si>
+    <t>Tintash</t>
+  </si>
+  <si>
+    <t>Python, Docker, GitHub Actions, FastAPI, MLflow, AWS, Model Deployment, CI/CD, Monitoring</t>
+  </si>
+  <si>
+    <t>PKR 100k-170k</t>
+  </si>
+  <si>
+    <t>i2c Inc</t>
+  </si>
+  <si>
+    <t>Python, OpenCV, PyTorch, CNNs, Image Classification, REST APIs, Docker, Feature Extraction</t>
+  </si>
+  <si>
+    <t>Python, BERT, SpaCy, Text Classification, Named Entity Recognition, REST APIs, Docker, PyTorch</t>
+  </si>
+  <si>
+    <t>LUMS (Lahore University)</t>
+  </si>
+  <si>
+    <t>Python, PyTorch, Research Writing, Deep Learning, NLP, Computer Vision, Grant Writing, Publishing</t>
+  </si>
+  <si>
+    <t>PKR 200k-400k</t>
+  </si>
+  <si>
+    <t>Academia</t>
+  </si>
+  <si>
+    <t>Packages Limited</t>
+  </si>
+  <si>
+    <t>Python, R, SQL, Statistics, Supply Chain Analytics, Operations Research, Machine Learning, Tableau</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Verafin Pakistan</t>
+  </si>
+  <si>
+    <t>Python, Java, REST APIs, PostgreSQL, Microservices, Kafka, Docker, Financial Crime Detection, AML</t>
+  </si>
+  <si>
+    <t>PKR 220k-380k</t>
+  </si>
+  <si>
+    <t>Hashe Computer Solutions</t>
+  </si>
+  <si>
+    <t>React, Python, Django, PostgreSQL, AWS, Docker, REST APIs, TypeScript, Agile, CI/CD</t>
+  </si>
+  <si>
+    <t>PKR 200k-360k</t>
+  </si>
+  <si>
+    <t>Softvision Pakistan</t>
+  </si>
+  <si>
+    <t>Python, Airflow, SQL, AWS, ETL, dbt, Data Quality, Spark, PostgreSQL, Docker</t>
+  </si>
+  <si>
+    <t>PKR 210k-360k</t>
+  </si>
+  <si>
+    <t>Dubizzle Labs (Pakistan)</t>
+  </si>
+  <si>
+    <t>Python, LLMs, LangChain, RAG, Embeddings, FastAPI, Docker, OpenAI API, Vector DBs</t>
+  </si>
+  <si>
+    <t>PKR 180k-320k</t>
+  </si>
+  <si>
+    <t>Python, Scikit-learn, TensorFlow, Feature Engineering, Model Deployment, REST APIs, Docker, SQL</t>
+  </si>
+  <si>
+    <t>Daraz (Alibaba Pakistan)</t>
+  </si>
+  <si>
+    <t>SQL, Python, Tableau, E-Commerce Analytics, Customer Analytics, Funnel Analysis, Power BI, KPI Reporting</t>
+  </si>
+  <si>
+    <t>Sendian Creations</t>
+  </si>
+  <si>
+    <t>Node.js, MongoDB, REST APIs, Docker, AWS, Redis, JWT, Stripe Integration, Microservices</t>
+  </si>
+  <si>
+    <t>PKR 130k-230k</t>
+  </si>
+  <si>
+    <t>Avanceon</t>
+  </si>
+  <si>
+    <t>SCADA Security, Network Security, OT Security, Penetration Testing, ICS, Firewalls, Linux, Python</t>
+  </si>
+  <si>
+    <t>Industrial</t>
+  </si>
+  <si>
+    <t>Xavor Corporation</t>
+  </si>
+  <si>
+    <t>Docker, Kubernetes, AWS, Terraform, CI/CD, Jenkins, Ansible, Linux, Monitoring, Shell Scripting</t>
+  </si>
+  <si>
+    <t>Rapidev</t>
+  </si>
+  <si>
+    <t>Python, LLMs, FastAPI, Docker, Embeddings, Vector DBs, RAG, LangChain, OpenAI API, AWS</t>
+  </si>
+  <si>
+    <t>PKR 90k-160k</t>
+  </si>
+  <si>
+    <t>Elastic</t>
+  </si>
+  <si>
+    <t>Python, Elasticsearch, NLP, Vector Search, Sparse Dense Retrieval, PyTorch, ML Ranking, REST APIs</t>
+  </si>
+  <si>
+    <t>Expedia</t>
+  </si>
+  <si>
+    <t>Python, SQL, Statistics, A/B Testing, Causal Inference, Machine Learning, Spark, Travel Demand Forecasting</t>
+  </si>
+  <si>
+    <t>Cloudflare</t>
+  </si>
+  <si>
+    <t>Go, Rust, Python, Distributed Systems, DNS, Edge Computing, Performance Optimization, Security</t>
+  </si>
+  <si>
+    <t>$155k-$210k</t>
+  </si>
+  <si>
+    <t>Figma</t>
+  </si>
+  <si>
+    <t>React, TypeScript, Node.js, WebAssembly, Canvas API, Collaboration Engine, PostgreSQL, WebSockets</t>
+  </si>
+  <si>
+    <t>Pinterest</t>
+  </si>
+  <si>
+    <t>Python, Kubeflow, GCP, Airflow, Feature Store, MLflow, Model Monitoring, Spark, BigQuery</t>
+  </si>
+  <si>
+    <t>$135k-$180k</t>
+  </si>
+  <si>
+    <t>Okta</t>
+  </si>
+  <si>
+    <t>IAM Security, Zero Trust, OAuth2, SAML, Python, Penetration Testing, Cloud Security, SIEM</t>
+  </si>
+  <si>
+    <t>$145k-$190k</t>
+  </si>
+  <si>
+    <t>Roblox</t>
+  </si>
+  <si>
+    <t>Python, Spark, Kafka, Airflow, AWS, dbt, Real Time Analytics, Data Modeling, Gaming Analytics</t>
+  </si>
+  <si>
+    <t>Gaming</t>
+  </si>
+  <si>
+    <t>Boston Dynamics</t>
+  </si>
+  <si>
+    <t>Python, C++, OpenCV, PyTorch, Robot Perception, SLAM, Depth Estimation, Real Time Systems, ROS</t>
+  </si>
+  <si>
+    <t>Robotics</t>
+  </si>
+  <si>
+    <t>Python, PyTorch, LLMs, Fine Tuning, Embeddings, Text Generation, RAG, Evaluation, PEFT, LoRA</t>
+  </si>
+  <si>
+    <t>$140k-$190k CAD</t>
+  </si>
+  <si>
+    <t>Stability AI</t>
+  </si>
+  <si>
+    <t>Python, PyTorch, Diffusion Models, LLMs, Image Generation, Fine Tuning, RLHF, Safety, Evaluation</t>
+  </si>
+  <si>
+    <t>£130k-£190k</t>
+  </si>
+  <si>
+    <t>Python, PyTorch, On-device AI, Privacy Preserving ML, Federated Learning, Neural Architecture</t>
+  </si>
+  <si>
+    <t>$175k-$255k</t>
+  </si>
+  <si>
+    <t>Python, SQL, Causal Inference, A/B Testing, E-Commerce Analytics, Machine Learning, dbt, Looker</t>
+  </si>
+  <si>
+    <t>$120k-$160k CAD</t>
+  </si>
+  <si>
+    <t>DoorDash</t>
+  </si>
+  <si>
+    <t>Go, Python, PostgreSQL, Kafka, Redis, Kubernetes, Microservices, Logistics APIs, gRPC, Docker</t>
+  </si>
+  <si>
+    <t>Vercel</t>
+  </si>
+  <si>
+    <t>React, Next.js, TypeScript, Node.js, Edge Functions, Serverless, PostgreSQL, CDN, CI/CD</t>
+  </si>
+  <si>
+    <t>Python, Docker, Kubernetes, GCP, CI/CD, Model Registry, Inference API, Transformers Library, FastAPI</t>
+  </si>
+  <si>
+    <t>Airbus</t>
+  </si>
+  <si>
+    <t>SQL, Python, Power BI, Aviation Analytics, Maintenance Data, Supply Chain Analytics, Statistical Analysis</t>
+  </si>
+  <si>
+    <t>Aerospace</t>
+  </si>
+  <si>
+    <t>Accenture</t>
+  </si>
+  <si>
+    <t>Risk Assessment, SOC Analysis, SIEM, Incident Response, Threat Intelligence, Compliance, Cloud Security</t>
+  </si>
+  <si>
+    <t>$75k-$105k</t>
+  </si>
+  <si>
+    <t>Robinhood</t>
+  </si>
+  <si>
+    <t>Python, Spark, Airflow, Kafka, dbt, Snowflake, Financial Data, Real Time Streaming, Data Quality</t>
+  </si>
+  <si>
+    <t>Snap Inc</t>
+  </si>
+  <si>
+    <t>Python, PyTorch, AR/AI Filters, Computer Vision, On-device ML, TFLite, Model Optimization, C++</t>
+  </si>
+  <si>
+    <t>Discord</t>
+  </si>
+  <si>
+    <t>React, TypeScript, Python, Elixir, PostgreSQL, WebSockets, REST APIs, Real Time Systems, AWS</t>
   </si>
 </sst>
 </file>
@@ -791,15 +2150,27 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -807,15 +2178,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1097,7 +2486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M146"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.21875" customWidth="1"/>
@@ -3001,6 +4390,4106 @@
         <v>108</v>
       </c>
     </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A47" s="4">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49" s="4">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A51" s="4">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53" s="4">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A55" s="4">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M55" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A57" s="4">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A59" s="4">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A60" s="3">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A61" s="4">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M61" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A62" s="3">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A63" s="4">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M63" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A65" s="4">
+        <v>64</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M65" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A66" s="3">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A67" s="4">
+        <v>66</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M67" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A68" s="3">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A69" s="4">
+        <v>68</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="M69" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A70" s="3">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A71" s="4">
+        <v>70</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M71" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A72" s="3">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A73" s="4">
+        <v>72</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M73" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A74" s="3">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M74" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A75" s="4">
+        <v>74</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M75" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A76" s="3">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A77" s="4">
+        <v>76</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M77" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A78" s="3">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A79" s="4">
+        <v>78</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M79" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A80" s="3">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A81" s="4">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L81" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M81" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A82" s="3">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M82" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A83" s="4">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M83" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A84" s="3">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L84" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M84" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A85" s="4">
+        <v>84</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M85" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A86" s="3">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L86" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" s="4">
+        <v>86</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L87" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M87" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A88" s="3">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M88" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89" s="4">
+        <v>88</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I89" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L89" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M89" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90" s="3">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L90" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M90" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A91" s="4">
+        <v>90</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L91" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M91" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A92" s="3">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L92" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M92" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A93" s="4">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L93" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M93" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A94" s="3">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A95" s="4">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L95" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M95" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A96" s="3">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A97" s="4">
+        <v>96</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L97" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M97" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A98" s="3">
+        <v>97</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L98" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M98" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A99" s="4">
+        <v>98</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L99" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M99" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A100" s="3">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A101" s="4">
+        <v>100</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L101" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M101" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A102" s="3">
+        <v>101</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A103" s="4">
+        <v>102</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L103" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M103" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A104" s="3">
+        <v>103</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K104" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L104" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M104" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A105" s="4">
+        <v>104</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K105" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L105" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M105" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A106" s="3">
+        <v>105</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L106" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M106" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A107" s="4">
+        <v>106</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J107" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K107" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L107" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M107" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A108" s="3">
+        <v>107</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J108" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K108" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L108" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M108" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A109" s="4">
+        <v>108</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J109" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K109" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L109" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="M109" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A110" s="3">
+        <v>109</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L110" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M110" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A111" s="4">
+        <v>110</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I111" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="J111" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K111" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L111" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="M111" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A112" s="3">
+        <v>111</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J112" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K112" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L112" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M112" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A113" s="4">
+        <v>112</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="J113" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K113" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L113" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M113" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A114" s="3">
+        <v>113</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K114" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L114" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M114" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A115" s="4">
+        <v>114</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I115" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K115" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L115" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M115" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A116" s="3">
+        <v>115</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K116" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L116" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M116" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A117" s="4">
+        <v>116</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="J117" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K117" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L117" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M117" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A118" s="3">
+        <v>117</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K118" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L118" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M118" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A119" s="4">
+        <v>118</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I119" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J119" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K119" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L119" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M119" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A120" s="3">
+        <v>119</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K120" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L120" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M120" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A121" s="4">
+        <v>120</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I121" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J121" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K121" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L121" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="M121" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A122" s="3">
+        <v>121</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J122" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K122" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L122" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M122" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A123" s="4">
+        <v>122</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I123" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J123" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K123" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L123" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M123" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A124" s="3">
+        <v>123</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K124" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L124" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M124" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A125" s="4">
+        <v>124</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G125" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I125" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J125" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K125" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L125" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M125" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A126" s="3">
+        <v>125</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K126" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L126" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M126" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A127" s="4">
+        <v>126</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J127" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K127" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L127" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M127" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A128" s="3">
+        <v>127</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J128" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K128" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L128" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M128" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A129" s="4">
+        <v>128</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="H129" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I129" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J129" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K129" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L129" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M129" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A130" s="3">
+        <v>129</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="J130" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K130" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L130" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M130" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A131" s="4">
+        <v>130</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I131" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J131" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K131" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L131" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M131" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A132" s="3">
+        <v>131</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="J132" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K132" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L132" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M132" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A133" s="4">
+        <v>132</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H133" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I133" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="J133" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K133" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L133" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M133" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A134" s="3">
+        <v>133</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="J134" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K134" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L134" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M134" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A135" s="4">
+        <v>134</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I135" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="J135" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K135" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L135" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M135" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A136" s="3">
+        <v>135</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J136" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K136" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L136" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M136" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A137" s="4">
+        <v>136</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I137" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J137" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K137" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L137" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="M137" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A138" s="3">
+        <v>137</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J138" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K138" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L138" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M138" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A139" s="4">
+        <v>138</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="E139" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H139" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I139" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="J139" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K139" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L139" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="M139" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A140" s="3">
+        <v>139</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J140" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K140" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L140" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M140" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A141" s="4">
+        <v>140</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G141" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="H141" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I141" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="J141" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K141" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L141" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M141" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A142" s="3">
+        <v>141</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="J142" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K142" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L142" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M142" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A143" s="4">
+        <v>142</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G143" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I143" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="J143" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K143" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L143" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="M143" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A144" s="3">
+        <v>143</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J144" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K144" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L144" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="M144" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A145" s="4">
+        <v>144</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="H145" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I145" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="J145" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K145" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="L145" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M145" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A146" s="3">
+        <v>145</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J146" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K146" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L146" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M146" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3008,11 +8497,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C3AF1BE-6BCA-4DEF-840A-8AC93AAD6043}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.109375" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="29.88671875" customWidth="1"/>
     <col min="4" max="4" width="67.88671875" customWidth="1"/>
     <col min="5" max="5" width="11.21875" customWidth="1"/>
     <col min="6" max="6" width="13.5546875" customWidth="1"/>
@@ -3342,6 +8831,1156 @@
         <v>32</v>
       </c>
     </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="4">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="4">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="4">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="4">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="4">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="4">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="4">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="4">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="4">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="4">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="4">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="3">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="4">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="3">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="4">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3349,12 +9988,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FB63CD8-B747-49AE-BA12-8744A7A76EE8}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="32.33203125" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="25.33203125" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -3378,7 +10018,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -3398,7 +10038,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -3418,7 +10058,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -3438,7 +10078,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -3458,7 +10098,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" t="s">
@@ -3478,7 +10118,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -3498,7 +10138,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -3518,7 +10158,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -3535,6 +10175,406 @@
       </c>
       <c r="F9" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
